--- a/files/energy/input/load_emulator/input_emulator_v2/2. usage_probability_v2.xlsx
+++ b/files/energy/input/load_emulator/input_emulator_v2/2. usage_probability_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rsericerca-my.sharepoint.com/personal/rollo_rse-web_it/Documents/Desktop/CACER simulator - public repo/CACER-simulator/files/energy/input/load_emulator/input_emulator_v2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="11_59AB53411A6BFA624CF54379889ED3FCF7CC7820" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{135FD8F0-3B0B-4A38-8E95-BD9919B262B2}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="11_59AB53411A6BFA624CF54379889ED3FCF7CC7820" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB95C969-1C2F-44BA-9DB4-DAF78843E9D1}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="working_day" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
     Information no available: equal to washing_machine</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
+    <comment ref="K1" authorId="3" shapeId="0" xr:uid="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -231,7 +231,7 @@
     Information no available: equal to washing_machine</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="3" shapeId="0" xr:uid="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
+    <comment ref="K1" authorId="3" shapeId="0" xr:uid="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -684,9 +684,6 @@
     <t>dehumidifier</t>
   </si>
   <si>
-    <t>electric_hob</t>
-  </si>
-  <si>
     <t>iron</t>
   </si>
   <si>
@@ -716,12 +713,15 @@
   <si>
     <t>screen</t>
   </si>
+  <si>
+    <t>induction_hob</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,12 +748,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1149,7 +1143,7 @@
   <threadedComment ref="H1" dT="2026-03-24T15:03:57.74" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{BC644381-17E1-42D6-9A9A-359FC117774B}">
     <text>Information no available: equal to washing_machine</text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
+  <threadedComment ref="K1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{345E653F-3282-4BB6-B2F9-944813E8D8A9}">
     <text>Zenodo db</text>
   </threadedComment>
   <threadedComment ref="L1" dT="2026-03-24T15:04:22.76" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{59AA8EEC-CCA3-46FB-A8BB-8FE1007B11EB}">
@@ -1202,7 +1196,7 @@
   <threadedComment ref="H1" dT="2026-03-24T15:03:57.74" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{07C19E1C-D168-4C85-A1C7-60F56A2E99CC}">
     <text>Information no available: equal to washing_machine</text>
   </threadedComment>
-  <threadedComment ref="I1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
+  <threadedComment ref="K1" dT="2026-03-24T15:04:07.09" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{12F2D9EA-8290-4EBD-95A0-22F667F8157D}">
     <text>Zenodo db</text>
   </threadedComment>
   <threadedComment ref="L1" dT="2026-03-24T15:04:22.76" personId="{E6CCC457-9E8F-4E28-A669-B1316F259632}" id="{C5E655D0-4EC1-4C75-AA79-9BF684AF2CD7}">
@@ -1252,8 +1246,9 @@
     <col min="1" max="1" width="8.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="12.77734375" style="6" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="12.77734375" style="6" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.77734375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="12.77734375" style="6" customWidth="1"/>
     <col min="14" max="14" width="19.44140625" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" style="6" bestFit="1" customWidth="1"/>
@@ -1292,31 +1287,31 @@
         <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>8</v>
@@ -1325,16 +1320,16 @@
         <v>9</v>
       </c>
       <c r="T1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>111</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X1" s="7" t="s">
         <v>10</v>
@@ -1343,13 +1338,13 @@
         <v>109</v>
       </c>
       <c r="Z1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="AC1" s="7" t="s">
         <v>11</v>
@@ -1478,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="I3" s="3">
-        <v>0</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="J3" s="3">
-        <v>5.5555555555555552E-2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -1670,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="I5" s="3">
-        <v>0</v>
+        <v>5.5555555555555552E-2</v>
       </c>
       <c r="J5" s="3">
-        <v>5.5555555555555552E-2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3">
         <v>0</v>
@@ -2822,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="I17" s="3">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3">
         <v>4.0832993058391182E-4</v>
-      </c>
-      <c r="J17" s="3">
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
       </c>
       <c r="L17" s="3">
         <f t="shared" si="1"/>
@@ -3110,13 +3105,13 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>4.0832993058391182E-4</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
       </c>
       <c r="L20" s="3">
         <f t="shared" si="1"/>
@@ -3206,13 +3201,13 @@
         <v>0</v>
       </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
         <v>4.0832993058391182E-4</v>
-      </c>
-      <c r="J21" s="3">
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
       </c>
       <c r="L21" s="3">
         <f t="shared" si="1"/>
@@ -3302,13 +3297,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>1.224989791751735E-3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="1"/>
@@ -3398,13 +3393,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>1.224989791751735E-3</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
       </c>
       <c r="L23" s="3">
         <f t="shared" si="1"/>
@@ -3494,13 +3489,13 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>2.8583095140873832E-3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="1"/>
@@ -3590,13 +3585,13 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
         <v>1.224989791751735E-3</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="1"/>
@@ -3686,13 +3681,13 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>6.5332788893425892E-3</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="1"/>
@@ -3782,13 +3777,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>4.8999591670069419E-3</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="1"/>
@@ -3878,13 +3873,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <v>8.1665986116782364E-3</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="1"/>
@@ -3974,13 +3969,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>8.9832584728460601E-3</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="1"/>
@@ -4070,13 +4065,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
         <v>1.3474887709269089E-2</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" si="1"/>
@@ -4166,13 +4161,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
         <v>1.9599836668027771E-2</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
-        <v>0</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" si="1"/>
@@ -4262,13 +4257,13 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>2.490812576561862E-2</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" si="1"/>
@@ -4358,13 +4353,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>2.368313597386688E-2</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
       </c>
       <c r="L33" s="3">
         <f t="shared" si="1"/>
@@ -4454,13 +4449,13 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
         <v>2.1641486320947329E-2</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
       </c>
       <c r="L34" s="3">
         <f t="shared" ref="L34:L65" si="7">1/96</f>
@@ -4550,13 +4545,13 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K35" s="3">
         <v>1.6333197223356469E-2</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L35" s="3">
         <f t="shared" si="7"/>
@@ -4646,13 +4641,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
         <v>1.5924867292772558E-2</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
       </c>
       <c r="L36" s="3">
         <f t="shared" si="7"/>
@@ -4742,13 +4737,13 @@
         <v>0</v>
       </c>
       <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3">
         <v>9.391588403429971E-3</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0</v>
       </c>
       <c r="L37" s="3">
         <f t="shared" si="7"/>
@@ -4838,13 +4833,13 @@
         <v>0</v>
       </c>
       <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+      <c r="K38" s="3">
         <v>1.0208248264597789E-2</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>0</v>
       </c>
       <c r="L38" s="3">
         <f t="shared" si="7"/>
@@ -4934,13 +4929,13 @@
         <v>0</v>
       </c>
       <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K39" s="3">
         <v>8.5749285422621474E-3</v>
-      </c>
-      <c r="J39" s="3">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L39" s="3">
         <f t="shared" si="7"/>
@@ -5030,13 +5025,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
         <v>9.7999183340138837E-3</v>
-      </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
-        <v>0</v>
       </c>
       <c r="L40" s="3">
         <f t="shared" si="7"/>
@@ -5126,13 +5121,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I41" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>5.7166190281747664E-3</v>
-      </c>
-      <c r="J41" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
       </c>
       <c r="L41" s="3">
         <f t="shared" si="7"/>
@@ -5222,13 +5217,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I42" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J42" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K42" s="3">
         <v>1.0616578195181711E-2</v>
-      </c>
-      <c r="J42" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K42" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L42" s="3">
         <f t="shared" si="7"/>
@@ -5318,13 +5313,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>2.3809523809523812E-2</v>
+      </c>
+      <c r="K43" s="3">
         <v>8.1665986116782364E-3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
-      <c r="K43" s="3">
-        <v>2.3809523809523812E-2</v>
       </c>
       <c r="L43" s="3">
         <f t="shared" si="7"/>
@@ -5414,13 +5409,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I44" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J44" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K44" s="3">
         <v>1.1433238056349529E-2</v>
-      </c>
-      <c r="J44" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K44" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L44" s="3">
         <f t="shared" si="7"/>
@@ -5510,13 +5505,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K45" s="3">
         <v>5.3082890975908537E-3</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L45" s="3">
         <f t="shared" si="7"/>
@@ -5606,13 +5601,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I46" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K46" s="3">
         <v>1.2658227848101271E-2</v>
-      </c>
-      <c r="J46" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L46" s="3">
         <f t="shared" si="7"/>
@@ -5702,13 +5697,13 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>1.0616578195181711E-2</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
       </c>
       <c r="L47" s="3">
         <f t="shared" si="7"/>
@@ -5798,13 +5793,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K48" s="3">
         <v>1.5516537362188649E-2</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L48" s="3">
         <f t="shared" si="7"/>
@@ -5894,13 +5889,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>1.5516537362188649E-2</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0</v>
-      </c>
-      <c r="K49" s="3">
-        <v>0</v>
       </c>
       <c r="L49" s="3">
         <f t="shared" si="7"/>
@@ -5990,13 +5985,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K50" s="3">
         <v>1.510820743160474E-2</v>
-      </c>
-      <c r="J50" s="3">
-        <v>0</v>
-      </c>
-      <c r="K50" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L50" s="3">
         <f t="shared" si="7"/>
@@ -6086,13 +6081,13 @@
         <v>0</v>
       </c>
       <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K51" s="3">
         <v>1.3474887709269089E-2</v>
-      </c>
-      <c r="J51" s="3">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L51" s="3">
         <f t="shared" si="7"/>
@@ -6182,13 +6177,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>1.8374846876276031E-2</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
       </c>
       <c r="L52" s="3">
         <f t="shared" si="7"/>
@@ -6278,13 +6273,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I53" s="3">
+        <v>0</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+      <c r="K53" s="3">
         <v>1.2249897917517349E-2</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0</v>
-      </c>
-      <c r="K53" s="3">
-        <v>0</v>
       </c>
       <c r="L53" s="3">
         <f t="shared" si="7"/>
@@ -6374,13 +6369,13 @@
         <v>0</v>
       </c>
       <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3">
         <v>1.8374846876276031E-2</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3">
-        <v>0</v>
       </c>
       <c r="L54" s="3">
         <f t="shared" si="7"/>
@@ -6470,13 +6465,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K55" s="3">
         <v>1.796651694569212E-2</v>
-      </c>
-      <c r="J55" s="3">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L55" s="3">
         <f t="shared" si="7"/>
@@ -6566,13 +6561,13 @@
         <v>0</v>
       </c>
       <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K56" s="3">
         <v>1.796651694569212E-2</v>
-      </c>
-      <c r="J56" s="3">
-        <v>0</v>
-      </c>
-      <c r="K56" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L56" s="3">
         <f t="shared" si="7"/>
@@ -6662,13 +6657,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>1.510820743160474E-2</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
       </c>
       <c r="L57" s="3">
         <f t="shared" si="7"/>
@@ -6758,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>1.510820743160474E-2</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
       </c>
       <c r="L58" s="3">
         <f t="shared" si="7"/>
@@ -6854,13 +6849,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>2.08248264597795E-2</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
       </c>
       <c r="L59" s="3">
         <f t="shared" si="7"/>
@@ -6950,13 +6945,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J60" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K60" s="3">
         <v>1.3474887709269089E-2</v>
-      </c>
-      <c r="J60" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K60" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L60" s="3">
         <f t="shared" si="7"/>
@@ -7046,13 +7041,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K61" s="3">
         <v>1.0616578195181711E-2</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L61" s="3">
         <f t="shared" si="7"/>
@@ -7142,13 +7137,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+      <c r="K62" s="3">
         <v>1.184156798693344E-2</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>0</v>
       </c>
       <c r="L62" s="3">
         <f t="shared" si="7"/>
@@ -7238,13 +7233,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K63" s="3">
         <v>1.4699877501020831E-2</v>
-      </c>
-      <c r="J63" s="3">
-        <v>0</v>
-      </c>
-      <c r="K63" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L63" s="3">
         <f t="shared" si="7"/>
@@ -7334,13 +7329,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J64" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K64" s="3">
         <v>9.391588403429971E-3</v>
-      </c>
-      <c r="J64" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K64" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L64" s="3">
         <f t="shared" si="7"/>
@@ -7430,13 +7425,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+      <c r="K65" s="3">
         <v>6.1249489587586773E-3</v>
-      </c>
-      <c r="J65" s="3">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3">
-        <v>0</v>
       </c>
       <c r="L65" s="3">
         <f t="shared" si="7"/>
@@ -7526,13 +7521,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
         <v>7.7582686810943246E-3</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
       </c>
       <c r="L66" s="3">
         <f t="shared" ref="L66:L97" si="13">1/96</f>
@@ -7622,13 +7617,13 @@
         <v>0</v>
       </c>
       <c r="I67" s="3">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J67" s="3">
+        <v>2.3809523809523812E-2</v>
+      </c>
+      <c r="K67" s="3">
         <v>1.0208248264597789E-2</v>
-      </c>
-      <c r="J67" s="3">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K67" s="3">
-        <v>2.3809523809523812E-2</v>
       </c>
       <c r="L67" s="3">
         <f t="shared" si="13"/>
@@ -7718,13 +7713,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I68" s="3">
+        <v>0</v>
+      </c>
+      <c r="J68" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K68" s="3">
         <v>7.3499387505104128E-3</v>
-      </c>
-      <c r="J68" s="3">
-        <v>0</v>
-      </c>
-      <c r="K68" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L68" s="3">
         <f t="shared" si="13"/>
@@ -7814,13 +7809,13 @@
         <v>5.7142857142857141E-2</v>
       </c>
       <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>2.3809523809523812E-2</v>
+      </c>
+      <c r="K69" s="3">
         <v>7.3499387505104128E-3</v>
-      </c>
-      <c r="J69" s="3">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3">
-        <v>2.3809523809523812E-2</v>
       </c>
       <c r="L69" s="3">
         <f t="shared" si="13"/>
@@ -7910,13 +7905,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K70" s="3">
         <v>6.941608819926501E-3</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L70" s="3">
         <f t="shared" si="13"/>
@@ -8006,13 +8001,13 @@
         <v>0</v>
       </c>
       <c r="I71" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K71" s="3">
         <v>7.3499387505104128E-3</v>
-      </c>
-      <c r="J71" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K71" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L71" s="3">
         <f t="shared" si="13"/>
@@ -8102,13 +8097,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I72" s="3">
+        <v>0</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K72" s="3">
         <v>1.0616578195181711E-2</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
-      </c>
-      <c r="K72" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L72" s="3">
         <f t="shared" si="13"/>
@@ -8198,13 +8193,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K73" s="3">
         <v>8.9832584728460601E-3</v>
-      </c>
-      <c r="J73" s="3">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L73" s="3">
         <f t="shared" si="13"/>
@@ -8294,13 +8289,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K74" s="3">
         <v>1.306655777868518E-2</v>
-      </c>
-      <c r="J74" s="3">
-        <v>0</v>
-      </c>
-      <c r="K74" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L74" s="3">
         <f t="shared" si="13"/>
@@ -8390,13 +8385,13 @@
         <v>0</v>
       </c>
       <c r="I75" s="3">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
+        <v>4.7619047619047623E-2</v>
+      </c>
+      <c r="K75" s="3">
         <v>1.7149857084524291E-2</v>
-      </c>
-      <c r="J75" s="3">
-        <v>0</v>
-      </c>
-      <c r="K75" s="3">
-        <v>4.7619047619047623E-2</v>
       </c>
       <c r="L75" s="3">
         <f t="shared" si="13"/>
@@ -8486,13 +8481,13 @@
         <v>0</v>
       </c>
       <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K76" s="3">
         <v>1.5516537362188649E-2</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L76" s="3">
         <f t="shared" si="13"/>
@@ -8582,13 +8577,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I77" s="3">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3">
+        <v>2.976190476190476E-2</v>
+      </c>
+      <c r="K77" s="3">
         <v>1.9599836668027771E-2</v>
-      </c>
-      <c r="J77" s="3">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3">
-        <v>2.976190476190476E-2</v>
       </c>
       <c r="L77" s="3">
         <f t="shared" si="13"/>
@@ -8678,13 +8673,13 @@
         <v>0</v>
       </c>
       <c r="I78" s="3">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="K78" s="3">
         <v>2.5724785626786439E-2</v>
-      </c>
-      <c r="J78" s="3">
-        <v>0</v>
-      </c>
-      <c r="K78" s="3">
-        <v>7.1428571428571425E-2</v>
       </c>
       <c r="L78" s="3">
         <f t="shared" si="13"/>
@@ -8774,13 +8769,13 @@
         <v>0</v>
       </c>
       <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K79" s="3">
         <v>3.1033074724377298E-2</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0</v>
-      </c>
-      <c r="K79" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L79" s="3">
         <f t="shared" si="13"/>
@@ -8870,13 +8865,13 @@
         <v>0</v>
       </c>
       <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>5.9523809523809521E-2</v>
+      </c>
+      <c r="K80" s="3">
         <v>3.3891384238464682E-2</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0</v>
-      </c>
-      <c r="K80" s="3">
-        <v>5.9523809523809521E-2</v>
       </c>
       <c r="L80" s="3">
         <f t="shared" si="13"/>
@@ -8966,13 +8961,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>4.7619047619047623E-2</v>
+      </c>
+      <c r="K81" s="3">
         <v>2.7766435279706E-2</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>4.7619047619047623E-2</v>
       </c>
       <c r="L81" s="3">
         <f t="shared" si="13"/>
@@ -9062,13 +9057,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I82" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J82" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K82" s="3">
         <v>2.7766435279706E-2</v>
-      </c>
-      <c r="J82" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K82" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L82" s="3">
         <f t="shared" si="13"/>
@@ -9158,13 +9153,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I83" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J83" s="3">
+        <v>5.3571428571428568E-2</v>
+      </c>
+      <c r="K83" s="3">
         <v>3.2258064516129031E-2</v>
-      </c>
-      <c r="J83" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K83" s="3">
-        <v>5.3571428571428568E-2</v>
       </c>
       <c r="L83" s="3">
         <f t="shared" si="13"/>
@@ -9254,13 +9249,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="3">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="J84" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K84" s="3">
         <v>3.1033074724377298E-2</v>
-      </c>
-      <c r="J84" s="3">
-        <v>5.5555555555555552E-2</v>
-      </c>
-      <c r="K84" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L84" s="3">
         <f t="shared" si="13"/>
@@ -9350,13 +9345,13 @@
         <v>0</v>
       </c>
       <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K85" s="3">
         <v>2.327480604328297E-2</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L85" s="3">
         <f t="shared" si="13"/>
@@ -9446,13 +9441,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="K86" s="3">
         <v>2.5316455696202531E-2</v>
-      </c>
-      <c r="J86" s="3">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3">
-        <v>3.5714285714285712E-2</v>
       </c>
       <c r="L86" s="3">
         <f t="shared" si="13"/>
@@ -9542,13 +9537,13 @@
         <v>0</v>
       </c>
       <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <v>2.976190476190476E-2</v>
+      </c>
+      <c r="K87" s="3">
         <v>2.08248264597795E-2</v>
-      </c>
-      <c r="J87" s="3">
-        <v>0</v>
-      </c>
-      <c r="K87" s="3">
-        <v>2.976190476190476E-2</v>
       </c>
       <c r="L87" s="3">
         <f t="shared" si="13"/>
@@ -9638,13 +9633,13 @@
         <v>0</v>
       </c>
       <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <v>4.1666666666666657E-2</v>
+      </c>
+      <c r="K88" s="3">
         <v>1.3883217639853E-2</v>
-      </c>
-      <c r="J88" s="3">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3">
-        <v>4.1666666666666657E-2</v>
       </c>
       <c r="L88" s="3">
         <f t="shared" si="13"/>
@@ -9734,13 +9729,13 @@
         <v>2.8571428571428571E-2</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>1.1433238056349529E-2</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>0</v>
       </c>
       <c r="L89" s="3">
         <f t="shared" si="13"/>
@@ -9830,13 +9825,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K90" s="3">
         <v>4.49162923642303E-3</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L90" s="3">
         <f t="shared" si="13"/>
@@ -9926,13 +9921,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>1.785714285714286E-2</v>
+      </c>
+      <c r="K91" s="3">
         <v>6.1249489587586773E-3</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>1.785714285714286E-2</v>
       </c>
       <c r="L91" s="3">
         <f t="shared" si="13"/>
@@ -10022,13 +10017,13 @@
         <v>0</v>
       </c>
       <c r="I92" s="3">
+        <v>0</v>
+      </c>
+      <c r="J92" s="3">
+        <v>1.1904761904761901E-2</v>
+      </c>
+      <c r="K92" s="3">
         <v>3.674969375255206E-3</v>
-      </c>
-      <c r="J92" s="3">
-        <v>0</v>
-      </c>
-      <c r="K92" s="3">
-        <v>1.1904761904761901E-2</v>
       </c>
       <c r="L92" s="3">
         <f t="shared" si="13"/>
@@ -10118,13 +10113,13 @@
         <v>0</v>
       </c>
       <c r="I93" s="3">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3">
+        <v>0</v>
+      </c>
+      <c r="K93" s="3">
         <v>6.1249489587586773E-3</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3">
-        <v>0</v>
       </c>
       <c r="L93" s="3">
         <f t="shared" si="13"/>
@@ -10214,13 +10209,13 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>5.9523809523809521E-3</v>
+      </c>
+      <c r="K94" s="3">
         <v>3.266639444671295E-3</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>5.9523809523809521E-3</v>
       </c>
       <c r="L94" s="3">
         <f t="shared" si="13"/>
@@ -10310,13 +10305,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3">
+        <v>0</v>
+      </c>
+      <c r="K95" s="3">
         <v>1.6333197223356471E-3</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3">
-        <v>0</v>
       </c>
       <c r="L95" s="3">
         <f t="shared" si="13"/>
@@ -10406,13 +10401,13 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>1.224989791751735E-3</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
       </c>
       <c r="L96" s="3">
         <f t="shared" si="13"/>
@@ -10502,13 +10497,13 @@
         <v>0</v>
       </c>
       <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3">
         <v>1.224989791751735E-3</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3">
-        <v>0</v>
       </c>
       <c r="L97" s="3">
         <f t="shared" si="13"/>
@@ -10587,7 +10582,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D97 G2:H97 J2:K97 Q2:S97 V2:Y97 AC2:AC97">
+  <conditionalFormatting sqref="C2:D97 G2:J97 Q2:S97 V2:Y97 AC2:AC97">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -10623,7 +10618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I97">
+  <conditionalFormatting sqref="K2:K97">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -10732,8 +10727,9 @@
     <col min="1" max="1" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="12.77734375" customWidth="1"/>
     <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="12.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="12.77734375" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="12.77734375" customWidth="1"/>
     <col min="14" max="14" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -10773,31 +10769,31 @@
         <v>3</v>
       </c>
       <c r="I1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>115</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>116</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R1" s="7" t="s">
         <v>8</v>
@@ -10806,16 +10802,16 @@
         <v>9</v>
       </c>
       <c r="T1" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="U1" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>111</v>
       </c>
       <c r="W1" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="X1" s="7" t="s">
         <v>10</v>
@@ -10824,13 +10820,13 @@
         <v>109</v>
       </c>
       <c r="Z1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>123</v>
       </c>
       <c r="AC1" s="7" t="s">
         <v>11</v>
@@ -12762,13 +12758,13 @@
         <v>0</v>
       </c>
       <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
         <v>1.9417475728155339E-3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
       </c>
       <c r="L22" s="3">
         <f t="shared" si="2"/>
@@ -12857,13 +12853,13 @@
         <v>0</v>
       </c>
       <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>1.9417475728155339E-3</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
       </c>
       <c r="L23" s="3">
         <f t="shared" si="2"/>
@@ -12952,13 +12948,13 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>2.9126213592233011E-3</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
       </c>
       <c r="L24" s="3">
         <f t="shared" si="2"/>
@@ -13047,13 +13043,13 @@
         <v>0</v>
       </c>
       <c r="I25" s="3">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3">
         <v>2.9126213592233011E-3</v>
-      </c>
-      <c r="J25" s="3">
-        <v>0</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0</v>
       </c>
       <c r="L25" s="3">
         <f t="shared" si="2"/>
@@ -13142,13 +13138,13 @@
         <v>0</v>
       </c>
       <c r="I26" s="3">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>3.8834951456310678E-3</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
       </c>
       <c r="L26" s="3">
         <f t="shared" si="2"/>
@@ -13237,13 +13233,13 @@
         <v>0</v>
       </c>
       <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>6.7961165048543689E-3</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
       </c>
       <c r="L27" s="3">
         <f t="shared" si="2"/>
@@ -13332,13 +13328,13 @@
         <v>0</v>
       </c>
       <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
         <v>6.7961165048543689E-3</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
-        <v>0</v>
       </c>
       <c r="L28" s="3">
         <f t="shared" si="2"/>
@@ -13427,13 +13423,13 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>7.7669902912621356E-3</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
       </c>
       <c r="L29" s="3">
         <f t="shared" si="2"/>
@@ -13522,13 +13518,13 @@
         <v>0</v>
       </c>
       <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
         <v>1.067961165048544E-2</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
       </c>
       <c r="L30" s="3">
         <f t="shared" si="2"/>
@@ -13617,13 +13613,13 @@
         <v>0</v>
       </c>
       <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3">
         <v>1.3592233009708739E-2</v>
-      </c>
-      <c r="J31" s="3">
-        <v>0</v>
-      </c>
-      <c r="K31" s="3">
-        <v>0</v>
       </c>
       <c r="L31" s="3">
         <f t="shared" si="2"/>
@@ -13712,13 +13708,13 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>2.135922330097087E-2</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
       </c>
       <c r="L32" s="3">
         <f t="shared" si="2"/>
@@ -13807,13 +13803,13 @@
         <v>0</v>
       </c>
       <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>2.2330097087378639E-2</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
       </c>
       <c r="L33" s="3">
         <f t="shared" si="2"/>
@@ -13902,13 +13898,13 @@
         <v>0</v>
       </c>
       <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
         <v>1.8446601941747569E-2</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>0</v>
       </c>
       <c r="L34" s="3">
         <f t="shared" si="2"/>
@@ -13997,13 +13993,13 @@
         <v>0</v>
       </c>
       <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>1.8446601941747569E-2</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>0</v>
       </c>
       <c r="L35" s="3">
         <f t="shared" si="2"/>
@@ -14092,13 +14088,13 @@
         <v>0</v>
       </c>
       <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
         <v>1.5533980582524269E-2</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>0</v>
       </c>
       <c r="L36" s="3">
         <f t="shared" si="2"/>
@@ -14187,13 +14183,13 @@
         <v>0.125</v>
       </c>
       <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K37" s="3">
         <v>8.7378640776699032E-3</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L37" s="3">
         <f t="shared" si="2"/>
@@ -14282,13 +14278,13 @@
         <v>0</v>
       </c>
       <c r="I38" s="3">
+        <v>0</v>
+      </c>
+      <c r="J38" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K38" s="3">
         <v>1.6504854368932041E-2</v>
-      </c>
-      <c r="J38" s="3">
-        <v>0</v>
-      </c>
-      <c r="K38" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L38" s="3">
         <f t="shared" si="2"/>
@@ -14377,13 +14373,13 @@
         <v>0</v>
       </c>
       <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0</v>
+      </c>
+      <c r="K39" s="3">
         <v>9.7087378640776691E-3</v>
-      </c>
-      <c r="J39" s="3">
-        <v>0</v>
-      </c>
-      <c r="K39" s="3">
-        <v>0</v>
       </c>
       <c r="L39" s="3">
         <f t="shared" si="2"/>
@@ -14472,13 +14468,13 @@
         <v>0.125</v>
       </c>
       <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K40" s="3">
         <v>1.3592233009708739E-2</v>
-      </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L40" s="3">
         <f t="shared" si="2"/>
@@ -14567,13 +14563,13 @@
         <v>0</v>
       </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
         <v>9.7087378640776691E-3</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
-        <v>0</v>
       </c>
       <c r="L41" s="3">
         <f t="shared" si="2"/>
@@ -14662,13 +14658,13 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>5.8252427184466021E-3</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
       </c>
       <c r="L42" s="3">
         <f t="shared" si="2"/>
@@ -14757,13 +14753,13 @@
         <v>0.125</v>
       </c>
       <c r="I43" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K43" s="3">
         <v>9.7087378640776691E-3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K43" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L43" s="3">
         <f t="shared" si="2"/>
@@ -14852,13 +14848,13 @@
         <v>0</v>
       </c>
       <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
         <v>9.7087378640776691E-3</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
       </c>
       <c r="L44" s="3">
         <f t="shared" si="2"/>
@@ -14947,13 +14943,13 @@
         <v>0</v>
       </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+      <c r="K45" s="3">
         <v>1.3592233009708739E-2</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
-      </c>
-      <c r="K45" s="3">
-        <v>0</v>
       </c>
       <c r="L45" s="3">
         <f t="shared" si="2"/>
@@ -15042,13 +15038,13 @@
         <v>0</v>
       </c>
       <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K46" s="3">
         <v>1.3592233009708739E-2</v>
-      </c>
-      <c r="J46" s="3">
-        <v>0</v>
-      </c>
-      <c r="K46" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L46" s="3">
         <f t="shared" si="2"/>
@@ -15137,13 +15133,13 @@
         <v>0</v>
       </c>
       <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+      <c r="K47" s="3">
         <v>5.8252427184466021E-3</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
-      </c>
-      <c r="K47" s="3">
-        <v>0</v>
       </c>
       <c r="L47" s="3">
         <f t="shared" si="2"/>
@@ -15232,13 +15228,13 @@
         <v>0</v>
       </c>
       <c r="I48" s="3">
+        <v>0</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K48" s="3">
         <v>1.1650485436893201E-2</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L48" s="3">
         <f t="shared" si="2"/>
@@ -15327,13 +15323,13 @@
         <v>0</v>
       </c>
       <c r="I49" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K49" s="3">
         <v>1.1650485436893201E-2</v>
-      </c>
-      <c r="J49" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K49" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L49" s="3">
         <f t="shared" si="2"/>
@@ -15422,13 +15418,13 @@
         <v>0</v>
       </c>
       <c r="I50" s="3">
+        <v>0</v>
+      </c>
+      <c r="J50" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K50" s="3">
         <v>2.135922330097087E-2</v>
-      </c>
-      <c r="J50" s="3">
-        <v>0</v>
-      </c>
-      <c r="K50" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L50" s="3">
         <f t="shared" si="2"/>
@@ -15517,13 +15513,13 @@
         <v>0.125</v>
       </c>
       <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K51" s="3">
         <v>2.0388349514563111E-2</v>
-      </c>
-      <c r="J51" s="3">
-        <v>0</v>
-      </c>
-      <c r="K51" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L51" s="3">
         <f t="shared" si="2"/>
@@ -15612,13 +15608,13 @@
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K52" s="3">
         <v>9.7087378640776691E-3</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L52" s="3">
         <f t="shared" si="2"/>
@@ -15707,13 +15703,13 @@
         <v>0</v>
       </c>
       <c r="I53" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="J53" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K53" s="3">
         <v>1.747572815533981E-2</v>
-      </c>
-      <c r="J53" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="K53" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L53" s="3">
         <f t="shared" si="2"/>
@@ -15802,13 +15798,13 @@
         <v>0</v>
       </c>
       <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K54" s="3">
         <v>1.747572815533981E-2</v>
-      </c>
-      <c r="J54" s="3">
-        <v>0</v>
-      </c>
-      <c r="K54" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L54" s="3">
         <f t="shared" si="2"/>
@@ -15897,13 +15893,13 @@
         <v>0</v>
       </c>
       <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K55" s="3">
         <v>2.621359223300971E-2</v>
-      </c>
-      <c r="J55" s="3">
-        <v>0</v>
-      </c>
-      <c r="K55" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L55" s="3">
         <f t="shared" si="2"/>
@@ -15992,13 +15988,13 @@
         <v>0.125</v>
       </c>
       <c r="I56" s="3">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K56" s="3">
         <v>1.1650485436893201E-2</v>
-      </c>
-      <c r="J56" s="3">
-        <v>0</v>
-      </c>
-      <c r="K56" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L56" s="3">
         <f t="shared" si="2"/>
@@ -16087,13 +16083,13 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K57" s="3">
         <v>2.524271844660194E-2</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L57" s="3">
         <f t="shared" si="2"/>
@@ -16182,13 +16178,13 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K58" s="3">
         <v>1.747572815533981E-2</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L58" s="3">
         <f t="shared" si="2"/>
@@ -16277,13 +16273,13 @@
         <v>0</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
         <v>1.262135922330097E-2</v>
-      </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3">
-        <v>0</v>
       </c>
       <c r="L59" s="3">
         <f t="shared" si="2"/>
@@ -16372,13 +16368,13 @@
         <v>0</v>
       </c>
       <c r="I60" s="3">
+        <v>0</v>
+      </c>
+      <c r="J60" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K60" s="3">
         <v>6.7961165048543689E-3</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
-      </c>
-      <c r="K60" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L60" s="3">
         <f t="shared" si="2"/>
@@ -16467,13 +16463,13 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
+        <v>5.7971014492753617E-2</v>
+      </c>
+      <c r="K61" s="3">
         <v>1.6504854368932041E-2</v>
-      </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
-      <c r="K61" s="3">
-        <v>5.7971014492753617E-2</v>
       </c>
       <c r="L61" s="3">
         <f t="shared" si="2"/>
@@ -16562,13 +16558,13 @@
         <v>0</v>
       </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K62" s="3">
         <v>7.7669902912621356E-3</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L62" s="3">
         <f t="shared" si="2"/>
@@ -16657,13 +16653,13 @@
         <v>0</v>
       </c>
       <c r="I63" s="3">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K63" s="3">
         <v>8.7378640776699032E-3</v>
-      </c>
-      <c r="J63" s="3">
-        <v>0</v>
-      </c>
-      <c r="K63" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L63" s="3">
         <f t="shared" si="2"/>
@@ -16752,13 +16748,13 @@
         <v>0</v>
       </c>
       <c r="I64" s="3">
+        <v>0</v>
+      </c>
+      <c r="J64" s="3">
+        <v>4.3478260869565223E-2</v>
+      </c>
+      <c r="K64" s="3">
         <v>1.067961165048544E-2</v>
-      </c>
-      <c r="J64" s="3">
-        <v>0</v>
-      </c>
-      <c r="K64" s="3">
-        <v>4.3478260869565223E-2</v>
       </c>
       <c r="L64" s="3">
         <f t="shared" si="2"/>
@@ -16847,13 +16843,13 @@
         <v>0</v>
       </c>
       <c r="I65" s="3">
+        <v>0</v>
+      </c>
+      <c r="J65" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K65" s="3">
         <v>1.262135922330097E-2</v>
-      </c>
-      <c r="J65" s="3">
-        <v>0</v>
-      </c>
-      <c r="K65" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L65" s="3">
         <f t="shared" si="2"/>
@@ -16942,13 +16938,13 @@
         <v>0</v>
       </c>
       <c r="I66" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+      <c r="K66" s="3">
         <v>8.7378640776699032E-3</v>
-      </c>
-      <c r="J66" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
       </c>
       <c r="L66" s="3">
         <f t="shared" si="2"/>
@@ -17037,13 +17033,13 @@
         <v>0.125</v>
       </c>
       <c r="I67" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J67" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K67" s="3">
         <v>8.7378640776699032E-3</v>
-      </c>
-      <c r="J67" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K67" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L67" s="3">
         <f t="shared" ref="L67:L97" si="7">1/96</f>
@@ -17132,13 +17128,13 @@
         <v>0</v>
       </c>
       <c r="I68" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3">
         <v>5.8252427184466021E-3</v>
-      </c>
-      <c r="J68" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K68" s="3">
-        <v>0</v>
       </c>
       <c r="L68" s="3">
         <f t="shared" si="7"/>
@@ -17227,13 +17223,13 @@
         <v>0</v>
       </c>
       <c r="I69" s="3">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0</v>
+      </c>
+      <c r="K69" s="3">
         <v>6.7961165048543689E-3</v>
-      </c>
-      <c r="J69" s="3">
-        <v>0</v>
-      </c>
-      <c r="K69" s="3">
-        <v>0</v>
       </c>
       <c r="L69" s="3">
         <f t="shared" si="7"/>
@@ -17322,13 +17318,13 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K70" s="3">
         <v>5.8252427184466021E-3</v>
-      </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
-      <c r="K70" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L70" s="3">
         <f t="shared" si="7"/>
@@ -17417,13 +17413,13 @@
         <v>0</v>
       </c>
       <c r="I71" s="3">
+        <v>0</v>
+      </c>
+      <c r="J71" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K71" s="3">
         <v>1.067961165048544E-2</v>
-      </c>
-      <c r="J71" s="3">
-        <v>0</v>
-      </c>
-      <c r="K71" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L71" s="3">
         <f t="shared" si="7"/>
@@ -17512,13 +17508,13 @@
         <v>0</v>
       </c>
       <c r="I72" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+      <c r="K72" s="3">
         <v>7.7669902912621356E-3</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K72" s="3">
-        <v>0</v>
       </c>
       <c r="L72" s="3">
         <f t="shared" si="7"/>
@@ -17607,13 +17603,13 @@
         <v>0</v>
       </c>
       <c r="I73" s="3">
+        <v>0</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0</v>
+      </c>
+      <c r="K73" s="3">
         <v>6.7961165048543689E-3</v>
-      </c>
-      <c r="J73" s="3">
-        <v>0</v>
-      </c>
-      <c r="K73" s="3">
-        <v>0</v>
       </c>
       <c r="L73" s="3">
         <f t="shared" si="7"/>
@@ -17702,13 +17698,13 @@
         <v>0</v>
       </c>
       <c r="I74" s="3">
+        <v>0</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0</v>
+      </c>
+      <c r="K74" s="3">
         <v>1.262135922330097E-2</v>
-      </c>
-      <c r="J74" s="3">
-        <v>0</v>
-      </c>
-      <c r="K74" s="3">
-        <v>0</v>
       </c>
       <c r="L74" s="3">
         <f t="shared" si="7"/>
@@ -17797,13 +17793,13 @@
         <v>0</v>
       </c>
       <c r="I75" s="3">
+        <v>0</v>
+      </c>
+      <c r="J75" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K75" s="3">
         <v>1.5533980582524269E-2</v>
-      </c>
-      <c r="J75" s="3">
-        <v>0</v>
-      </c>
-      <c r="K75" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L75" s="3">
         <f t="shared" si="7"/>
@@ -17892,13 +17888,13 @@
         <v>0.125</v>
       </c>
       <c r="I76" s="3">
+        <v>0</v>
+      </c>
+      <c r="J76" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K76" s="3">
         <v>1.6504854368932041E-2</v>
-      </c>
-      <c r="J76" s="3">
-        <v>0</v>
-      </c>
-      <c r="K76" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L76" s="3">
         <f t="shared" si="7"/>
@@ -17987,13 +17983,13 @@
         <v>0</v>
       </c>
       <c r="I77" s="3">
+        <v>0</v>
+      </c>
+      <c r="J77" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K77" s="3">
         <v>1.5533980582524269E-2</v>
-      </c>
-      <c r="J77" s="3">
-        <v>0</v>
-      </c>
-      <c r="K77" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L77" s="3">
         <f t="shared" si="7"/>
@@ -18082,13 +18078,13 @@
         <v>0</v>
       </c>
       <c r="I78" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J78" s="3">
+        <v>0</v>
+      </c>
+      <c r="K78" s="3">
         <v>2.9126213592233011E-2</v>
-      </c>
-      <c r="J78" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K78" s="3">
-        <v>0</v>
       </c>
       <c r="L78" s="3">
         <f t="shared" si="7"/>
@@ -18177,13 +18173,13 @@
         <v>0</v>
       </c>
       <c r="I79" s="3">
+        <v>0</v>
+      </c>
+      <c r="J79" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K79" s="3">
         <v>2.7184466019417479E-2</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0</v>
-      </c>
-      <c r="K79" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L79" s="3">
         <f t="shared" si="7"/>
@@ -18272,13 +18268,13 @@
         <v>0</v>
       </c>
       <c r="I80" s="3">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3">
+        <v>4.3478260869565223E-2</v>
+      </c>
+      <c r="K80" s="3">
         <v>3.8834951456310683E-2</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0</v>
-      </c>
-      <c r="K80" s="3">
-        <v>4.3478260869565223E-2</v>
       </c>
       <c r="L80" s="3">
         <f t="shared" si="7"/>
@@ -18367,13 +18363,13 @@
         <v>0</v>
       </c>
       <c r="I81" s="3">
+        <v>0</v>
+      </c>
+      <c r="J81" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K81" s="3">
         <v>2.524271844660194E-2</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L81" s="3">
         <f t="shared" si="7"/>
@@ -18462,13 +18458,13 @@
         <v>0</v>
       </c>
       <c r="I82" s="3">
+        <v>0</v>
+      </c>
+      <c r="J82" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K82" s="3">
         <v>3.1067961165048539E-2</v>
-      </c>
-      <c r="J82" s="3">
-        <v>0</v>
-      </c>
-      <c r="K82" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L82" s="3">
         <f t="shared" si="7"/>
@@ -18557,13 +18553,13 @@
         <v>0</v>
       </c>
       <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K83" s="3">
         <v>2.621359223300971E-2</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L83" s="3">
         <f t="shared" si="7"/>
@@ -18652,13 +18648,13 @@
         <v>0</v>
       </c>
       <c r="I84" s="3">
+        <v>0</v>
+      </c>
+      <c r="J84" s="3">
+        <v>5.7971014492753617E-2</v>
+      </c>
+      <c r="K84" s="3">
         <v>2.524271844660194E-2</v>
-      </c>
-      <c r="J84" s="3">
-        <v>0</v>
-      </c>
-      <c r="K84" s="3">
-        <v>5.7971014492753617E-2</v>
       </c>
       <c r="L84" s="3">
         <f t="shared" si="7"/>
@@ -18747,13 +18743,13 @@
         <v>0.125</v>
       </c>
       <c r="I85" s="3">
+        <v>0</v>
+      </c>
+      <c r="J85" s="3">
+        <v>4.3478260869565223E-2</v>
+      </c>
+      <c r="K85" s="3">
         <v>2.3300970873786409E-2</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0</v>
-      </c>
-      <c r="K85" s="3">
-        <v>4.3478260869565223E-2</v>
       </c>
       <c r="L85" s="3">
         <f t="shared" si="7"/>
@@ -18842,13 +18838,13 @@
         <v>0</v>
       </c>
       <c r="I86" s="3">
+        <v>0</v>
+      </c>
+      <c r="J86" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K86" s="3">
         <v>3.4951456310679613E-2</v>
-      </c>
-      <c r="J86" s="3">
-        <v>0</v>
-      </c>
-      <c r="K86" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L86" s="3">
         <f t="shared" si="7"/>
@@ -18937,13 +18933,13 @@
         <v>0</v>
       </c>
       <c r="I87" s="3">
+        <v>0</v>
+      </c>
+      <c r="J87" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K87" s="3">
         <v>1.8446601941747569E-2</v>
-      </c>
-      <c r="J87" s="3">
-        <v>0</v>
-      </c>
-      <c r="K87" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L87" s="3">
         <f t="shared" si="7"/>
@@ -19032,13 +19028,13 @@
         <v>0</v>
       </c>
       <c r="I88" s="3">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3">
+        <v>2.8985507246376808E-2</v>
+      </c>
+      <c r="K88" s="3">
         <v>1.8446601941747569E-2</v>
-      </c>
-      <c r="J88" s="3">
-        <v>0</v>
-      </c>
-      <c r="K88" s="3">
-        <v>2.8985507246376808E-2</v>
       </c>
       <c r="L88" s="3">
         <f t="shared" si="7"/>
@@ -19127,13 +19123,13 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K89" s="3">
         <v>1.067961165048544E-2</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L89" s="3">
         <f t="shared" si="7"/>
@@ -19222,13 +19218,13 @@
         <v>0</v>
       </c>
       <c r="I90" s="3">
+        <v>0</v>
+      </c>
+      <c r="J90" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K90" s="3">
         <v>4.8543689320388354E-3</v>
-      </c>
-      <c r="J90" s="3">
-        <v>0</v>
-      </c>
-      <c r="K90" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L90" s="3">
         <f t="shared" si="7"/>
@@ -19317,13 +19313,13 @@
         <v>0</v>
       </c>
       <c r="I91" s="3">
+        <v>0</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>1.067961165048544E-2</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
       </c>
       <c r="L91" s="3">
         <f t="shared" si="7"/>
@@ -19412,13 +19408,13 @@
         <v>0</v>
       </c>
       <c r="I92" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+      <c r="K92" s="3">
         <v>6.7961165048543689E-3</v>
-      </c>
-      <c r="J92" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="K92" s="3">
-        <v>0</v>
       </c>
       <c r="L92" s="3">
         <f t="shared" si="7"/>
@@ -19507,13 +19503,13 @@
         <v>0</v>
       </c>
       <c r="I93" s="3">
+        <v>0</v>
+      </c>
+      <c r="J93" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K93" s="3">
         <v>2.9126213592233011E-3</v>
-      </c>
-      <c r="J93" s="3">
-        <v>0</v>
-      </c>
-      <c r="K93" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L93" s="3">
         <f t="shared" si="7"/>
@@ -19602,13 +19598,13 @@
         <v>0</v>
       </c>
       <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+      <c r="K94" s="3">
         <v>3.8834951456310678E-3</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3">
-        <v>0</v>
       </c>
       <c r="L94" s="3">
         <f t="shared" si="7"/>
@@ -19697,13 +19693,13 @@
         <v>0</v>
       </c>
       <c r="I95" s="3">
+        <v>0</v>
+      </c>
+      <c r="J95" s="3">
+        <v>1.4492753623188409E-2</v>
+      </c>
+      <c r="K95" s="3">
         <v>1.9417475728155339E-3</v>
-      </c>
-      <c r="J95" s="3">
-        <v>0</v>
-      </c>
-      <c r="K95" s="3">
-        <v>1.4492753623188409E-2</v>
       </c>
       <c r="L95" s="3">
         <f t="shared" si="7"/>
@@ -19795,10 +19791,10 @@
         <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>1.4492753623188409E-2</v>
       </c>
       <c r="K96" s="3">
-        <v>1.4492753623188409E-2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="3">
         <f t="shared" si="7"/>
@@ -19887,13 +19883,13 @@
         <v>0</v>
       </c>
       <c r="I97" s="3">
+        <v>0</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+      <c r="K97" s="3">
         <v>9.7087378640776695E-4</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-      <c r="K97" s="3">
-        <v>0</v>
       </c>
       <c r="L97" s="3">
         <f t="shared" si="7"/>
@@ -19975,7 +19971,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:D97 F2:H97 J2:L97 Q2:V97 Y2:AC97">
+  <conditionalFormatting sqref="C2:D97 F2:J97 L2:L97 Q2:V97 Y2:AC97">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -19999,7 +19995,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I97">
+  <conditionalFormatting sqref="K2:K97">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
